--- a/Team-Data/2013-14/3-2-2013-14.xlsx
+++ b/Team-Data/2013-14/3-2-2013-14.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -661,70 +728,70 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E2" t="n">
         <v>26</v>
       </c>
       <c r="F2" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G2" t="n">
-        <v>0.448</v>
+        <v>0.456</v>
       </c>
       <c r="H2" t="n">
         <v>48.4</v>
       </c>
       <c r="I2" t="n">
-        <v>37.8</v>
+        <v>37.7</v>
       </c>
       <c r="J2" t="n">
-        <v>82.09999999999999</v>
+        <v>82</v>
       </c>
       <c r="K2" t="n">
-        <v>0.46</v>
+        <v>0.459</v>
       </c>
       <c r="L2" t="n">
-        <v>9.6</v>
+        <v>9.5</v>
       </c>
       <c r="M2" t="n">
-        <v>25.1</v>
+        <v>24.9</v>
       </c>
       <c r="N2" t="n">
-        <v>0.381</v>
+        <v>0.38</v>
       </c>
       <c r="O2" t="n">
-        <v>16.8</v>
+        <v>16.7</v>
       </c>
       <c r="P2" t="n">
-        <v>21.6</v>
+        <v>21.5</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.777</v>
+        <v>0.779</v>
       </c>
       <c r="R2" t="n">
         <v>9</v>
       </c>
       <c r="S2" t="n">
-        <v>31.4</v>
+        <v>31.5</v>
       </c>
       <c r="T2" t="n">
-        <v>40.4</v>
+        <v>40.5</v>
       </c>
       <c r="U2" t="n">
         <v>25.2</v>
       </c>
       <c r="V2" t="n">
-        <v>15.3</v>
+        <v>15.4</v>
       </c>
       <c r="W2" t="n">
         <v>8.6</v>
       </c>
       <c r="X2" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="Y2" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="Z2" t="n">
         <v>18.9</v>
@@ -733,13 +800,13 @@
         <v>19.4</v>
       </c>
       <c r="AB2" t="n">
-        <v>101.9</v>
+        <v>101.5</v>
       </c>
       <c r="AC2" t="n">
-        <v>-0.4</v>
+        <v>-0.2</v>
       </c>
       <c r="AD2" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="AE2" t="n">
         <v>18</v>
@@ -751,10 +818,10 @@
         <v>18</v>
       </c>
       <c r="AH2" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AI2" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AJ2" t="n">
         <v>22</v>
@@ -778,10 +845,10 @@
         <v>22</v>
       </c>
       <c r="AQ2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AR2" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AS2" t="n">
         <v>19</v>
@@ -793,7 +860,7 @@
         <v>1</v>
       </c>
       <c r="AV2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AW2" t="n">
         <v>7</v>
@@ -802,7 +869,7 @@
         <v>23</v>
       </c>
       <c r="AY2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AZ2" t="n">
         <v>4</v>
@@ -811,7 +878,7 @@
         <v>26</v>
       </c>
       <c r="BB2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BC2" t="n">
         <v>16</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>3-2-2013-14</t>
+          <t>2014-03-02</t>
         </is>
       </c>
     </row>
@@ -921,7 +988,7 @@
         <v>-3.6</v>
       </c>
       <c r="AD3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AE3" t="n">
         <v>25</v>
@@ -975,7 +1042,7 @@
         <v>26</v>
       </c>
       <c r="AV3" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AW3" t="n">
         <v>22</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>3-2-2013-14</t>
+          <t>2014-03-02</t>
         </is>
       </c>
     </row>
@@ -1103,7 +1170,7 @@
         <v>-2.2</v>
       </c>
       <c r="AD4" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AE4" t="n">
         <v>16</v>
@@ -1127,7 +1194,7 @@
         <v>15</v>
       </c>
       <c r="AL4" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AM4" t="n">
         <v>12</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>3-2-2013-14</t>
+          <t>2014-03-02</t>
         </is>
       </c>
     </row>
@@ -1207,25 +1274,25 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E5" t="n">
         <v>27</v>
       </c>
       <c r="F5" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G5" t="n">
-        <v>0.458</v>
+        <v>0.466</v>
       </c>
       <c r="H5" t="n">
         <v>48.3</v>
       </c>
       <c r="I5" t="n">
-        <v>35.4</v>
+        <v>35.5</v>
       </c>
       <c r="J5" t="n">
-        <v>81.3</v>
+        <v>81.5</v>
       </c>
       <c r="K5" t="n">
         <v>0.436</v>
@@ -1234,34 +1301,34 @@
         <v>5.8</v>
       </c>
       <c r="M5" t="n">
-        <v>16.5</v>
+        <v>16.4</v>
       </c>
       <c r="N5" t="n">
-        <v>0.351</v>
+        <v>0.35</v>
       </c>
       <c r="O5" t="n">
-        <v>18.4</v>
+        <v>18.2</v>
       </c>
       <c r="P5" t="n">
-        <v>25.2</v>
+        <v>25</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.729</v>
+        <v>0.728</v>
       </c>
       <c r="R5" t="n">
-        <v>9</v>
+        <v>9.1</v>
       </c>
       <c r="S5" t="n">
-        <v>33</v>
+        <v>33.1</v>
       </c>
       <c r="T5" t="n">
-        <v>42</v>
+        <v>42.2</v>
       </c>
       <c r="U5" t="n">
         <v>21</v>
       </c>
       <c r="V5" t="n">
-        <v>12.6</v>
+        <v>12.5</v>
       </c>
       <c r="W5" t="n">
         <v>6.2</v>
@@ -1270,22 +1337,22 @@
         <v>5.1</v>
       </c>
       <c r="Y5" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="Z5" t="n">
-        <v>18.3</v>
+        <v>18.2</v>
       </c>
       <c r="AA5" t="n">
-        <v>21.3</v>
+        <v>21.1</v>
       </c>
       <c r="AB5" t="n">
         <v>95</v>
       </c>
       <c r="AC5" t="n">
-        <v>-2</v>
+        <v>-1.7</v>
       </c>
       <c r="AD5" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="AE5" t="n">
         <v>17</v>
@@ -1297,7 +1364,7 @@
         <v>17</v>
       </c>
       <c r="AH5" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AI5" t="n">
         <v>27</v>
@@ -1315,7 +1382,7 @@
         <v>28</v>
       </c>
       <c r="AN5" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AO5" t="n">
         <v>12</v>
@@ -1324,16 +1391,16 @@
         <v>7</v>
       </c>
       <c r="AQ5" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AR5" t="n">
         <v>27</v>
       </c>
       <c r="AS5" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AT5" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AU5" t="n">
         <v>19</v>
@@ -1348,13 +1415,13 @@
         <v>11</v>
       </c>
       <c r="AY5" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AZ5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BA5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BB5" t="n">
         <v>27</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>3-2-2013-14</t>
+          <t>2014-03-02</t>
         </is>
       </c>
     </row>
@@ -1389,31 +1456,31 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E6" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F6" t="n">
         <v>26</v>
       </c>
       <c r="G6" t="n">
-        <v>0.5590000000000001</v>
+        <v>0.552</v>
       </c>
       <c r="H6" t="n">
         <v>48.7</v>
       </c>
       <c r="I6" t="n">
-        <v>34.6</v>
+        <v>34.5</v>
       </c>
       <c r="J6" t="n">
-        <v>80.59999999999999</v>
+        <v>80.5</v>
       </c>
       <c r="K6" t="n">
-        <v>0.429</v>
+        <v>0.428</v>
       </c>
       <c r="L6" t="n">
-        <v>6.1</v>
+        <v>6</v>
       </c>
       <c r="M6" t="n">
         <v>17.6</v>
@@ -1422,13 +1489,13 @@
         <v>0.344</v>
       </c>
       <c r="O6" t="n">
-        <v>18.2</v>
+        <v>18.1</v>
       </c>
       <c r="P6" t="n">
-        <v>23.5</v>
+        <v>23.4</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.772</v>
+        <v>0.773</v>
       </c>
       <c r="R6" t="n">
         <v>12.1</v>
@@ -1440,10 +1507,10 @@
         <v>45.2</v>
       </c>
       <c r="U6" t="n">
-        <v>22.4</v>
+        <v>22.3</v>
       </c>
       <c r="V6" t="n">
-        <v>15.6</v>
+        <v>15.8</v>
       </c>
       <c r="W6" t="n">
         <v>7.3</v>
@@ -1452,25 +1519,25 @@
         <v>5.3</v>
       </c>
       <c r="Y6" t="n">
-        <v>6.2</v>
+        <v>6.3</v>
       </c>
       <c r="Z6" t="n">
-        <v>19.1</v>
+        <v>19.2</v>
       </c>
       <c r="AA6" t="n">
-        <v>21.3</v>
+        <v>21.2</v>
       </c>
       <c r="AB6" t="n">
-        <v>93.3</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
       <c r="AD6" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="AE6" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AF6" t="n">
         <v>12</v>
@@ -1497,7 +1564,7 @@
         <v>27</v>
       </c>
       <c r="AN6" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AO6" t="n">
         <v>13</v>
@@ -1512,7 +1579,7 @@
         <v>6</v>
       </c>
       <c r="AS6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AT6" t="n">
         <v>7</v>
@@ -1521,13 +1588,13 @@
         <v>11</v>
       </c>
       <c r="AV6" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AW6" t="n">
         <v>20</v>
       </c>
       <c r="AX6" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AY6" t="n">
         <v>29</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>3-2-2013-14</t>
+          <t>2014-03-02</t>
         </is>
       </c>
     </row>
@@ -1649,7 +1716,7 @@
         <v>-4.2</v>
       </c>
       <c r="AD7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE7" t="n">
         <v>20</v>
@@ -1664,7 +1731,7 @@
         <v>2</v>
       </c>
       <c r="AI7" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AJ7" t="n">
         <v>5</v>
@@ -1673,13 +1740,13 @@
         <v>30</v>
       </c>
       <c r="AL7" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AM7" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AN7" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AO7" t="n">
         <v>15</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>3-2-2013-14</t>
+          <t>2014-03-02</t>
         </is>
       </c>
     </row>
@@ -1753,25 +1820,25 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E8" t="n">
         <v>36</v>
       </c>
       <c r="F8" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G8" t="n">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="H8" t="n">
         <v>48.1</v>
       </c>
       <c r="I8" t="n">
-        <v>39.5</v>
+        <v>39.4</v>
       </c>
       <c r="J8" t="n">
-        <v>83.59999999999999</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="K8" t="n">
         <v>0.473</v>
@@ -1780,37 +1847,37 @@
         <v>8.5</v>
       </c>
       <c r="M8" t="n">
-        <v>22.5</v>
+        <v>22.6</v>
       </c>
       <c r="N8" t="n">
         <v>0.377</v>
       </c>
       <c r="O8" t="n">
-        <v>16.9</v>
+        <v>17</v>
       </c>
       <c r="P8" t="n">
-        <v>21.1</v>
+        <v>21.3</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.8</v>
+        <v>0.802</v>
       </c>
       <c r="R8" t="n">
-        <v>10.1</v>
+        <v>10</v>
       </c>
       <c r="S8" t="n">
         <v>30.3</v>
       </c>
       <c r="T8" t="n">
-        <v>40.4</v>
+        <v>40.3</v>
       </c>
       <c r="U8" t="n">
         <v>23.7</v>
       </c>
       <c r="V8" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="W8" t="n">
-        <v>8.9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="X8" t="n">
         <v>4.2</v>
@@ -1822,28 +1889,28 @@
         <v>20.1</v>
       </c>
       <c r="AA8" t="n">
-        <v>19.5</v>
+        <v>19.6</v>
       </c>
       <c r="AB8" t="n">
         <v>104.4</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="AD8" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AE8" t="n">
         <v>8</v>
       </c>
       <c r="AF8" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AG8" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AH8" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AI8" t="n">
         <v>3</v>
@@ -1885,7 +1952,7 @@
         <v>4</v>
       </c>
       <c r="AV8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AW8" t="n">
         <v>3</v>
@@ -1897,13 +1964,13 @@
         <v>3</v>
       </c>
       <c r="AZ8" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BA8" t="n">
         <v>24</v>
       </c>
       <c r="BB8" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BC8" t="n">
         <v>12</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>3-2-2013-14</t>
+          <t>2014-03-02</t>
         </is>
       </c>
     </row>
@@ -2013,7 +2080,7 @@
         <v>-2.5</v>
       </c>
       <c r="AD9" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="AE9" t="n">
         <v>19</v>
@@ -2031,7 +2098,7 @@
         <v>17</v>
       </c>
       <c r="AJ9" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AK9" t="n">
         <v>22</v>
@@ -2064,10 +2131,10 @@
         <v>5</v>
       </c>
       <c r="AU9" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AV9" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AW9" t="n">
         <v>24</v>
@@ -2079,7 +2146,7 @@
         <v>23</v>
       </c>
       <c r="AZ9" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BA9" t="n">
         <v>7</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>3-2-2013-14</t>
+          <t>2014-03-02</t>
         </is>
       </c>
     </row>
@@ -2195,7 +2262,7 @@
         <v>-2.8</v>
       </c>
       <c r="AD10" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AE10" t="n">
         <v>21</v>
@@ -2207,7 +2274,7 @@
         <v>21</v>
       </c>
       <c r="AH10" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="AI10" t="n">
         <v>5</v>
@@ -2258,7 +2325,7 @@
         <v>10</v>
       </c>
       <c r="AY10" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AZ10" t="n">
         <v>15</v>
@@ -2270,7 +2337,7 @@
         <v>15</v>
       </c>
       <c r="BC10" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BD10" t="n">
         <v>10</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>3-2-2013-14</t>
+          <t>2014-03-02</t>
         </is>
       </c>
     </row>
@@ -2299,16 +2366,16 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E11" t="n">
         <v>36</v>
       </c>
       <c r="F11" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G11" t="n">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="H11" t="n">
         <v>48.3</v>
@@ -2317,10 +2384,10 @@
         <v>38.8</v>
       </c>
       <c r="J11" t="n">
-        <v>85.2</v>
+        <v>85.09999999999999</v>
       </c>
       <c r="K11" t="n">
-        <v>0.455</v>
+        <v>0.456</v>
       </c>
       <c r="L11" t="n">
         <v>9.199999999999999</v>
@@ -2329,7 +2396,7 @@
         <v>24.4</v>
       </c>
       <c r="N11" t="n">
-        <v>0.377</v>
+        <v>0.378</v>
       </c>
       <c r="O11" t="n">
         <v>16.5</v>
@@ -2338,13 +2405,13 @@
         <v>22.1</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.746</v>
+        <v>0.745</v>
       </c>
       <c r="R11" t="n">
-        <v>11.3</v>
+        <v>11.2</v>
       </c>
       <c r="S11" t="n">
-        <v>34.5</v>
+        <v>34.6</v>
       </c>
       <c r="T11" t="n">
         <v>45.8</v>
@@ -2368,16 +2435,16 @@
         <v>22</v>
       </c>
       <c r="AA11" t="n">
-        <v>20</v>
+        <v>20.1</v>
       </c>
       <c r="AB11" t="n">
-        <v>103.3</v>
+        <v>103.4</v>
       </c>
       <c r="AC11" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="AD11" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AE11" t="n">
         <v>8</v>
@@ -2389,13 +2456,13 @@
         <v>8</v>
       </c>
       <c r="AH11" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="AI11" t="n">
         <v>7</v>
       </c>
       <c r="AJ11" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AK11" t="n">
         <v>10</v>
@@ -2431,7 +2498,7 @@
         <v>10</v>
       </c>
       <c r="AV11" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AW11" t="n">
         <v>13</v>
@@ -2443,16 +2510,16 @@
         <v>10</v>
       </c>
       <c r="AZ11" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BA11" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BB11" t="n">
         <v>10</v>
       </c>
       <c r="BC11" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BD11" t="n">
         <v>10</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>3-2-2013-14</t>
+          <t>2014-03-02</t>
         </is>
       </c>
     </row>
@@ -2559,7 +2626,7 @@
         <v>4.6</v>
       </c>
       <c r="AD12" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AE12" t="n">
         <v>7</v>
@@ -2571,10 +2638,10 @@
         <v>6</v>
       </c>
       <c r="AH12" t="n">
+        <v>15</v>
+      </c>
+      <c r="AI12" t="n">
         <v>14</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>15</v>
       </c>
       <c r="AJ12" t="n">
         <v>28</v>
@@ -2610,7 +2677,7 @@
         <v>6</v>
       </c>
       <c r="AU12" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AV12" t="n">
         <v>29</v>
@@ -2619,7 +2686,7 @@
         <v>18</v>
       </c>
       <c r="AX12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AY12" t="n">
         <v>20</v>
@@ -2634,7 +2701,7 @@
         <v>3</v>
       </c>
       <c r="BC12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BD12" t="n">
         <v>10</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>3-2-2013-14</t>
+          <t>2014-03-02</t>
         </is>
       </c>
     </row>
@@ -2663,61 +2730,61 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E13" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F13" t="n">
         <v>13</v>
       </c>
       <c r="G13" t="n">
-        <v>0.78</v>
+        <v>0.776</v>
       </c>
       <c r="H13" t="n">
         <v>48.3</v>
       </c>
       <c r="I13" t="n">
-        <v>36.9</v>
+        <v>37</v>
       </c>
       <c r="J13" t="n">
-        <v>81.3</v>
+        <v>81.2</v>
       </c>
       <c r="K13" t="n">
-        <v>0.454</v>
+        <v>0.455</v>
       </c>
       <c r="L13" t="n">
         <v>6.8</v>
       </c>
       <c r="M13" t="n">
-        <v>19.3</v>
+        <v>19.4</v>
       </c>
       <c r="N13" t="n">
         <v>0.353</v>
       </c>
       <c r="O13" t="n">
-        <v>18.5</v>
+        <v>18.4</v>
       </c>
       <c r="P13" t="n">
-        <v>23.7</v>
+        <v>23.6</v>
       </c>
       <c r="Q13" t="n">
         <v>0.781</v>
       </c>
       <c r="R13" t="n">
-        <v>10.4</v>
+        <v>10.3</v>
       </c>
       <c r="S13" t="n">
-        <v>35.2</v>
+        <v>35.3</v>
       </c>
       <c r="T13" t="n">
-        <v>45.5</v>
+        <v>45.6</v>
       </c>
       <c r="U13" t="n">
         <v>20.5</v>
       </c>
       <c r="V13" t="n">
-        <v>15.2</v>
+        <v>15.3</v>
       </c>
       <c r="W13" t="n">
         <v>7.2</v>
@@ -2726,22 +2793,22 @@
         <v>5.7</v>
       </c>
       <c r="Y13" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="Z13" t="n">
         <v>20.1</v>
       </c>
       <c r="AA13" t="n">
-        <v>22</v>
+        <v>21.9</v>
       </c>
       <c r="AB13" t="n">
-        <v>99.09999999999999</v>
+        <v>99.2</v>
       </c>
       <c r="AC13" t="n">
-        <v>7.9</v>
+        <v>8</v>
       </c>
       <c r="AD13" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="AE13" t="n">
         <v>1</v>
@@ -2762,7 +2829,7 @@
         <v>25</v>
       </c>
       <c r="AK13" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AL13" t="n">
         <v>21</v>
@@ -2777,7 +2844,7 @@
         <v>11</v>
       </c>
       <c r="AP13" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AQ13" t="n">
         <v>5</v>
@@ -2789,7 +2856,7 @@
         <v>1</v>
       </c>
       <c r="AT13" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AU13" t="n">
         <v>24</v>
@@ -2801,16 +2868,16 @@
         <v>21</v>
       </c>
       <c r="AX13" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AY13" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AZ13" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BA13" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BB13" t="n">
         <v>19</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>3-2-2013-14</t>
+          <t>2014-03-02</t>
         </is>
       </c>
     </row>
@@ -2923,7 +2990,7 @@
         <v>6.5</v>
       </c>
       <c r="AD14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE14" t="n">
         <v>5</v>
@@ -2938,7 +3005,7 @@
         <v>23</v>
       </c>
       <c r="AI14" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AJ14" t="n">
         <v>23</v>
@@ -2953,7 +3020,7 @@
         <v>8</v>
       </c>
       <c r="AN14" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AO14" t="n">
         <v>2</v>
@@ -2962,7 +3029,7 @@
         <v>2</v>
       </c>
       <c r="AQ14" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AR14" t="n">
         <v>21</v>
@@ -2998,7 +3065,7 @@
         <v>2</v>
       </c>
       <c r="BC14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BD14" t="n">
         <v>10</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>3-2-2013-14</t>
+          <t>2014-03-02</t>
         </is>
       </c>
     </row>
@@ -3105,13 +3172,13 @@
         <v>-5.4</v>
       </c>
       <c r="AD15" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AE15" t="n">
         <v>25</v>
       </c>
       <c r="AF15" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AG15" t="n">
         <v>25</v>
@@ -3132,7 +3199,7 @@
         <v>2</v>
       </c>
       <c r="AM15" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AN15" t="n">
         <v>3</v>
@@ -3168,7 +3235,7 @@
         <v>3</v>
       </c>
       <c r="AY15" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AZ15" t="n">
         <v>12</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>3-2-2013-14</t>
+          <t>2014-03-02</t>
         </is>
       </c>
     </row>
@@ -3287,13 +3354,13 @@
         <v>0.6</v>
       </c>
       <c r="AD16" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="AE16" t="n">
         <v>11</v>
       </c>
       <c r="AF16" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AG16" t="n">
         <v>11</v>
@@ -3302,13 +3369,13 @@
         <v>13</v>
       </c>
       <c r="AI16" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AJ16" t="n">
         <v>21</v>
       </c>
       <c r="AK16" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AL16" t="n">
         <v>30</v>
@@ -3317,7 +3384,7 @@
         <v>30</v>
       </c>
       <c r="AN16" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AO16" t="n">
         <v>29</v>
@@ -3335,19 +3402,19 @@
         <v>22</v>
       </c>
       <c r="AT16" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AU16" t="n">
         <v>13</v>
       </c>
       <c r="AV16" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW16" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AX16" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AY16" t="n">
         <v>21</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>3-2-2013-14</t>
+          <t>2014-03-02</t>
         </is>
       </c>
     </row>
@@ -3472,7 +3539,7 @@
         <v>30</v>
       </c>
       <c r="AE17" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AF17" t="n">
         <v>2</v>
@@ -3499,7 +3566,7 @@
         <v>15</v>
       </c>
       <c r="AN17" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AO17" t="n">
         <v>14</v>
@@ -3541,7 +3608,7 @@
         <v>12</v>
       </c>
       <c r="BB17" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BC17" t="n">
         <v>4</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>3-2-2013-14</t>
+          <t>2014-03-02</t>
         </is>
       </c>
     </row>
@@ -3651,7 +3718,7 @@
         <v>-8.699999999999999</v>
       </c>
       <c r="AD18" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="AE18" t="n">
         <v>30</v>
@@ -3690,7 +3757,7 @@
         <v>27</v>
       </c>
       <c r="AQ18" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AR18" t="n">
         <v>12</v>
@@ -3717,7 +3784,7 @@
         <v>19</v>
       </c>
       <c r="AZ18" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BA18" t="n">
         <v>17</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>3-2-2013-14</t>
+          <t>2014-03-02</t>
         </is>
       </c>
     </row>
@@ -3833,7 +3900,7 @@
         <v>4.1</v>
       </c>
       <c r="AD19" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="AE19" t="n">
         <v>15</v>
@@ -3872,16 +3939,16 @@
         <v>3</v>
       </c>
       <c r="AQ19" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AR19" t="n">
         <v>2</v>
       </c>
       <c r="AS19" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AT19" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AU19" t="n">
         <v>8</v>
@@ -3899,7 +3966,7 @@
         <v>26</v>
       </c>
       <c r="AZ19" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BA19" t="n">
         <v>3</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>3-2-2013-14</t>
+          <t>2014-03-02</t>
         </is>
       </c>
     </row>
@@ -4015,7 +4082,7 @@
         <v>-2.9</v>
       </c>
       <c r="AD20" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AE20" t="n">
         <v>21</v>
@@ -4027,7 +4094,7 @@
         <v>21</v>
       </c>
       <c r="AH20" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AI20" t="n">
         <v>13</v>
@@ -4036,7 +4103,7 @@
         <v>14</v>
       </c>
       <c r="AK20" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AL20" t="n">
         <v>27</v>
@@ -4054,7 +4121,7 @@
         <v>18</v>
       </c>
       <c r="AQ20" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AR20" t="n">
         <v>7</v>
@@ -4063,7 +4130,7 @@
         <v>26</v>
       </c>
       <c r="AT20" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AU20" t="n">
         <v>17</v>
@@ -4084,13 +4151,13 @@
         <v>27</v>
       </c>
       <c r="BA20" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BB20" t="n">
         <v>20</v>
       </c>
       <c r="BC20" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BD20" t="n">
         <v>10</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>3-2-2013-14</t>
+          <t>2014-03-02</t>
         </is>
       </c>
     </row>
@@ -4119,16 +4186,16 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E21" t="n">
         <v>21</v>
       </c>
       <c r="F21" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G21" t="n">
-        <v>0.35</v>
+        <v>0.356</v>
       </c>
       <c r="H21" t="n">
         <v>48.6</v>
@@ -4146,10 +4213,10 @@
         <v>9</v>
       </c>
       <c r="M21" t="n">
-        <v>24.5</v>
+        <v>24.6</v>
       </c>
       <c r="N21" t="n">
-        <v>0.365</v>
+        <v>0.367</v>
       </c>
       <c r="O21" t="n">
         <v>14.8</v>
@@ -4158,16 +4225,16 @@
         <v>19.7</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.752</v>
+        <v>0.751</v>
       </c>
       <c r="R21" t="n">
         <v>10.9</v>
       </c>
       <c r="S21" t="n">
-        <v>30</v>
+        <v>29.9</v>
       </c>
       <c r="T21" t="n">
-        <v>40.9</v>
+        <v>40.8</v>
       </c>
       <c r="U21" t="n">
         <v>20.3</v>
@@ -4176,28 +4243,28 @@
         <v>13.2</v>
       </c>
       <c r="W21" t="n">
-        <v>7.6</v>
+        <v>7.7</v>
       </c>
       <c r="X21" t="n">
         <v>4.5</v>
       </c>
       <c r="Y21" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="Z21" t="n">
-        <v>22.3</v>
+        <v>22.2</v>
       </c>
       <c r="AA21" t="n">
-        <v>19.6</v>
+        <v>19.7</v>
       </c>
       <c r="AB21" t="n">
-        <v>97.59999999999999</v>
+        <v>97.7</v>
       </c>
       <c r="AC21" t="n">
-        <v>-3</v>
+        <v>-2.7</v>
       </c>
       <c r="AD21" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AE21" t="n">
         <v>23</v>
@@ -4224,7 +4291,7 @@
         <v>7</v>
       </c>
       <c r="AM21" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AN21" t="n">
         <v>11</v>
@@ -4236,7 +4303,7 @@
         <v>30</v>
       </c>
       <c r="AQ21" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AR21" t="n">
         <v>19</v>
@@ -4254,7 +4321,7 @@
         <v>2</v>
       </c>
       <c r="AW21" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AX21" t="n">
         <v>20</v>
@@ -4266,13 +4333,13 @@
         <v>26</v>
       </c>
       <c r="BA21" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="BB21" t="n">
         <v>21</v>
       </c>
       <c r="BC21" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="BD21" t="n">
         <v>10</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>3-2-2013-14</t>
+          <t>2014-03-02</t>
         </is>
       </c>
     </row>
@@ -4301,16 +4368,16 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E22" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F22" t="n">
         <v>15</v>
       </c>
       <c r="G22" t="n">
-        <v>0.75</v>
+        <v>0.746</v>
       </c>
       <c r="H22" t="n">
         <v>48.2</v>
@@ -4322,7 +4389,7 @@
         <v>82.2</v>
       </c>
       <c r="K22" t="n">
-        <v>0.475</v>
+        <v>0.474</v>
       </c>
       <c r="L22" t="n">
         <v>7.5</v>
@@ -4331,16 +4398,16 @@
         <v>20.9</v>
       </c>
       <c r="N22" t="n">
-        <v>0.359</v>
+        <v>0.358</v>
       </c>
       <c r="O22" t="n">
-        <v>19.6</v>
+        <v>19.4</v>
       </c>
       <c r="P22" t="n">
-        <v>24.3</v>
+        <v>24.2</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.805</v>
+        <v>0.803</v>
       </c>
       <c r="R22" t="n">
         <v>11.1</v>
@@ -4364,22 +4431,22 @@
         <v>6.1</v>
       </c>
       <c r="Y22" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="Z22" t="n">
-        <v>21.8</v>
+        <v>21.7</v>
       </c>
       <c r="AA22" t="n">
-        <v>20.1</v>
+        <v>20</v>
       </c>
       <c r="AB22" t="n">
-        <v>105.1</v>
+        <v>104.9</v>
       </c>
       <c r="AC22" t="n">
-        <v>6.5</v>
+        <v>6.3</v>
       </c>
       <c r="AD22" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AE22" t="n">
         <v>2</v>
@@ -4388,7 +4455,7 @@
         <v>3</v>
       </c>
       <c r="AG22" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AH22" t="n">
         <v>26</v>
@@ -4397,7 +4464,7 @@
         <v>6</v>
       </c>
       <c r="AJ22" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AK22" t="n">
         <v>4</v>
@@ -4430,7 +4497,7 @@
         <v>8</v>
       </c>
       <c r="AU22" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AV22" t="n">
         <v>28</v>
@@ -4445,16 +4512,16 @@
         <v>4</v>
       </c>
       <c r="AZ22" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BA22" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BB22" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BC22" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BD22" t="n">
         <v>10</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>3-2-2013-14</t>
+          <t>2014-03-02</t>
         </is>
       </c>
     </row>
@@ -4483,22 +4550,22 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E23" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F23" t="n">
         <v>43</v>
       </c>
       <c r="G23" t="n">
-        <v>0.306</v>
+        <v>0.295</v>
       </c>
       <c r="H23" t="n">
         <v>48.7</v>
       </c>
       <c r="I23" t="n">
-        <v>36.6</v>
+        <v>36.7</v>
       </c>
       <c r="J23" t="n">
         <v>83</v>
@@ -4507,22 +4574,22 @@
         <v>0.442</v>
       </c>
       <c r="L23" t="n">
-        <v>6.9</v>
+        <v>7</v>
       </c>
       <c r="M23" t="n">
-        <v>19.8</v>
+        <v>19.9</v>
       </c>
       <c r="N23" t="n">
-        <v>0.349</v>
+        <v>0.352</v>
       </c>
       <c r="O23" t="n">
-        <v>16.5</v>
+        <v>16.4</v>
       </c>
       <c r="P23" t="n">
-        <v>21.5</v>
+        <v>21.4</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.765</v>
+        <v>0.764</v>
       </c>
       <c r="R23" t="n">
         <v>9.5</v>
@@ -4543,7 +4610,7 @@
         <v>7.7</v>
       </c>
       <c r="X23" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="Y23" t="n">
         <v>5.8</v>
@@ -4552,13 +4619,13 @@
         <v>19.9</v>
       </c>
       <c r="AA23" t="n">
-        <v>18.9</v>
+        <v>18.8</v>
       </c>
       <c r="AB23" t="n">
-        <v>96.59999999999999</v>
+        <v>96.7</v>
       </c>
       <c r="AC23" t="n">
-        <v>-5</v>
+        <v>-5.2</v>
       </c>
       <c r="AD23" t="n">
         <v>1</v>
@@ -4573,7 +4640,7 @@
         <v>28</v>
       </c>
       <c r="AH23" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AI23" t="n">
         <v>22</v>
@@ -4582,43 +4649,43 @@
         <v>16</v>
       </c>
       <c r="AK23" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AL23" t="n">
+        <v>19</v>
+      </c>
+      <c r="AM23" t="n">
         <v>20</v>
       </c>
-      <c r="AM23" t="n">
-        <v>21</v>
-      </c>
       <c r="AN23" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="AO23" t="n">
         <v>23</v>
       </c>
       <c r="AP23" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AQ23" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AR23" t="n">
         <v>24</v>
       </c>
       <c r="AS23" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AT23" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AU23" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AV23" t="n">
         <v>12</v>
       </c>
       <c r="AW23" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AX23" t="n">
         <v>25</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>3-2-2013-14</t>
+          <t>2014-03-02</t>
         </is>
       </c>
     </row>
@@ -4665,28 +4732,28 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E24" t="n">
         <v>15</v>
       </c>
       <c r="F24" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="G24" t="n">
-        <v>0.25</v>
+        <v>0.254</v>
       </c>
       <c r="H24" t="n">
         <v>48.6</v>
       </c>
       <c r="I24" t="n">
-        <v>38.2</v>
+        <v>38.3</v>
       </c>
       <c r="J24" t="n">
-        <v>88.2</v>
+        <v>88.3</v>
       </c>
       <c r="K24" t="n">
-        <v>0.433</v>
+        <v>0.434</v>
       </c>
       <c r="L24" t="n">
         <v>6.7</v>
@@ -4695,16 +4762,16 @@
         <v>21.9</v>
       </c>
       <c r="N24" t="n">
-        <v>0.306</v>
+        <v>0.308</v>
       </c>
       <c r="O24" t="n">
-        <v>16.8</v>
+        <v>16.9</v>
       </c>
       <c r="P24" t="n">
         <v>23.6</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.714</v>
+        <v>0.715</v>
       </c>
       <c r="R24" t="n">
         <v>11.9</v>
@@ -4713,13 +4780,13 @@
         <v>32.1</v>
       </c>
       <c r="T24" t="n">
-        <v>44</v>
+        <v>43.9</v>
       </c>
       <c r="U24" t="n">
-        <v>22</v>
+        <v>22.1</v>
       </c>
       <c r="V24" t="n">
-        <v>17.4</v>
+        <v>17.3</v>
       </c>
       <c r="W24" t="n">
         <v>9.199999999999999</v>
@@ -4728,7 +4795,7 @@
         <v>4.1</v>
       </c>
       <c r="Y24" t="n">
-        <v>7.3</v>
+        <v>7.4</v>
       </c>
       <c r="Z24" t="n">
         <v>21.8</v>
@@ -4737,13 +4804,13 @@
         <v>20.7</v>
       </c>
       <c r="AB24" t="n">
-        <v>99.90000000000001</v>
+        <v>100.3</v>
       </c>
       <c r="AC24" t="n">
         <v>-10.8</v>
       </c>
       <c r="AD24" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AE24" t="n">
         <v>29</v>
@@ -4779,7 +4846,7 @@
         <v>19</v>
       </c>
       <c r="AP24" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AQ24" t="n">
         <v>28</v>
@@ -4809,13 +4876,13 @@
         <v>30</v>
       </c>
       <c r="AZ24" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BA24" t="n">
         <v>13</v>
       </c>
       <c r="BB24" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BC24" t="n">
         <v>30</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>3-2-2013-14</t>
+          <t>2014-03-02</t>
         </is>
       </c>
     </row>
@@ -4847,46 +4914,46 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E25" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F25" t="n">
         <v>24</v>
       </c>
       <c r="G25" t="n">
-        <v>0.593</v>
+        <v>0.586</v>
       </c>
       <c r="H25" t="n">
         <v>48.3</v>
       </c>
       <c r="I25" t="n">
-        <v>38.7</v>
+        <v>38.6</v>
       </c>
       <c r="J25" t="n">
         <v>84.2</v>
       </c>
       <c r="K25" t="n">
-        <v>0.46</v>
+        <v>0.458</v>
       </c>
       <c r="L25" t="n">
-        <v>9.300000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="M25" t="n">
-        <v>25.1</v>
+        <v>25.2</v>
       </c>
       <c r="N25" t="n">
-        <v>0.372</v>
+        <v>0.367</v>
       </c>
       <c r="O25" t="n">
-        <v>18.6</v>
+        <v>18.5</v>
       </c>
       <c r="P25" t="n">
-        <v>24.5</v>
+        <v>24.4</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.761</v>
+        <v>0.759</v>
       </c>
       <c r="R25" t="n">
         <v>11.6</v>
@@ -4898,7 +4965,7 @@
         <v>43.3</v>
       </c>
       <c r="U25" t="n">
-        <v>19.2</v>
+        <v>19.1</v>
       </c>
       <c r="V25" t="n">
         <v>15.2</v>
@@ -4919,34 +4986,34 @@
         <v>21.2</v>
       </c>
       <c r="AB25" t="n">
-        <v>105.3</v>
+        <v>104.9</v>
       </c>
       <c r="AC25" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="AD25" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="AE25" t="n">
         <v>10</v>
       </c>
       <c r="AF25" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AG25" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AH25" t="n">
         <v>19</v>
       </c>
       <c r="AI25" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AJ25" t="n">
         <v>9</v>
       </c>
       <c r="AK25" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AL25" t="n">
         <v>4</v>
@@ -4955,7 +5022,7 @@
         <v>2</v>
       </c>
       <c r="AN25" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AO25" t="n">
         <v>10</v>
@@ -4991,13 +5058,13 @@
         <v>9</v>
       </c>
       <c r="AZ25" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BA25" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BB25" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BC25" t="n">
         <v>11</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>3-2-2013-14</t>
+          <t>2014-03-02</t>
         </is>
       </c>
     </row>
@@ -5107,7 +5174,7 @@
         <v>4.9</v>
       </c>
       <c r="AD26" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AE26" t="n">
         <v>5</v>
@@ -5119,7 +5186,7 @@
         <v>5</v>
       </c>
       <c r="AH26" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AI26" t="n">
         <v>2</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>3-2-2013-14</t>
+          <t>2014-03-02</t>
         </is>
       </c>
     </row>
@@ -5289,13 +5356,13 @@
         <v>-2.5</v>
       </c>
       <c r="AD27" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AE27" t="n">
         <v>25</v>
       </c>
       <c r="AF27" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AG27" t="n">
         <v>25</v>
@@ -5316,10 +5383,10 @@
         <v>24</v>
       </c>
       <c r="AM27" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AN27" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AO27" t="n">
         <v>4</v>
@@ -5328,7 +5395,7 @@
         <v>4</v>
       </c>
       <c r="AQ27" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AR27" t="n">
         <v>8</v>
@@ -5361,7 +5428,7 @@
         <v>4</v>
       </c>
       <c r="BB27" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BC27" t="n">
         <v>20</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>3-2-2013-14</t>
+          <t>2014-03-02</t>
         </is>
       </c>
     </row>
@@ -5393,16 +5460,16 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E28" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F28" t="n">
         <v>16</v>
       </c>
       <c r="G28" t="n">
-        <v>0.729</v>
+        <v>0.724</v>
       </c>
       <c r="H28" t="n">
         <v>48.3</v>
@@ -5420,22 +5487,22 @@
         <v>8</v>
       </c>
       <c r="M28" t="n">
-        <v>20.6</v>
+        <v>20.4</v>
       </c>
       <c r="N28" t="n">
         <v>0.39</v>
       </c>
       <c r="O28" t="n">
-        <v>15.7</v>
+        <v>15.6</v>
       </c>
       <c r="P28" t="n">
-        <v>20</v>
+        <v>19.9</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.786</v>
+        <v>0.784</v>
       </c>
       <c r="R28" t="n">
-        <v>9</v>
+        <v>8.9</v>
       </c>
       <c r="S28" t="n">
         <v>33.4</v>
@@ -5459,19 +5526,19 @@
         <v>4.8</v>
       </c>
       <c r="Z28" t="n">
-        <v>18</v>
+        <v>18.1</v>
       </c>
       <c r="AA28" t="n">
-        <v>19.5</v>
+        <v>19.4</v>
       </c>
       <c r="AB28" t="n">
-        <v>104</v>
+        <v>103.8</v>
       </c>
       <c r="AC28" t="n">
         <v>6</v>
       </c>
       <c r="AD28" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="AE28" t="n">
         <v>3</v>
@@ -5489,22 +5556,22 @@
         <v>1</v>
       </c>
       <c r="AJ28" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AK28" t="n">
         <v>2</v>
       </c>
       <c r="AL28" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AM28" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AN28" t="n">
         <v>1</v>
       </c>
       <c r="AO28" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AP28" t="n">
         <v>29</v>
@@ -5513,7 +5580,7 @@
         <v>4</v>
       </c>
       <c r="AR28" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="AS28" t="n">
         <v>6</v>
@@ -5534,7 +5601,7 @@
         <v>12</v>
       </c>
       <c r="AY28" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AZ28" t="n">
         <v>1</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>3-2-2013-14</t>
+          <t>2014-03-02</t>
         </is>
       </c>
     </row>
@@ -5575,16 +5642,16 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E29" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F29" t="n">
         <v>26</v>
       </c>
       <c r="G29" t="n">
-        <v>0.5590000000000001</v>
+        <v>0.552</v>
       </c>
       <c r="H29" t="n">
         <v>48.7</v>
@@ -5593,16 +5660,16 @@
         <v>36.4</v>
       </c>
       <c r="J29" t="n">
-        <v>82.5</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="K29" t="n">
-        <v>0.441</v>
+        <v>0.44</v>
       </c>
       <c r="L29" t="n">
         <v>8.300000000000001</v>
       </c>
       <c r="M29" t="n">
-        <v>22.9</v>
+        <v>23</v>
       </c>
       <c r="N29" t="n">
         <v>0.363</v>
@@ -5614,7 +5681,7 @@
         <v>24.6</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.776</v>
+        <v>0.775</v>
       </c>
       <c r="R29" t="n">
         <v>11.8</v>
@@ -5623,16 +5690,16 @@
         <v>31.3</v>
       </c>
       <c r="T29" t="n">
-        <v>43</v>
+        <v>43.1</v>
       </c>
       <c r="U29" t="n">
-        <v>21.4</v>
+        <v>21.2</v>
       </c>
       <c r="V29" t="n">
         <v>14.1</v>
       </c>
       <c r="W29" t="n">
-        <v>6.9</v>
+        <v>7</v>
       </c>
       <c r="X29" t="n">
         <v>4.3</v>
@@ -5641,22 +5708,22 @@
         <v>4.6</v>
       </c>
       <c r="Z29" t="n">
-        <v>22.8</v>
+        <v>22.9</v>
       </c>
       <c r="AA29" t="n">
         <v>22</v>
       </c>
       <c r="AB29" t="n">
-        <v>100.2</v>
+        <v>100.1</v>
       </c>
       <c r="AC29" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="AD29" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="AE29" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AF29" t="n">
         <v>12</v>
@@ -5668,7 +5735,7 @@
         <v>4</v>
       </c>
       <c r="AI29" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AJ29" t="n">
         <v>18</v>
@@ -5692,7 +5759,7 @@
         <v>9</v>
       </c>
       <c r="AQ29" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AR29" t="n">
         <v>10</v>
@@ -5716,16 +5783,16 @@
         <v>22</v>
       </c>
       <c r="AY29" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AZ29" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BA29" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BB29" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BC29" t="n">
         <v>10</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>3-2-2013-14</t>
+          <t>2014-03-02</t>
         </is>
       </c>
     </row>
@@ -5757,16 +5824,16 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E30" t="n">
         <v>21</v>
       </c>
       <c r="F30" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G30" t="n">
-        <v>0.356</v>
+        <v>0.362</v>
       </c>
       <c r="H30" t="n">
         <v>48.2</v>
@@ -5784,25 +5851,25 @@
         <v>6.8</v>
       </c>
       <c r="M30" t="n">
-        <v>19</v>
+        <v>19.1</v>
       </c>
       <c r="N30" t="n">
-        <v>0.356</v>
+        <v>0.355</v>
       </c>
       <c r="O30" t="n">
         <v>16.3</v>
       </c>
       <c r="P30" t="n">
-        <v>21.7</v>
+        <v>21.8</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.749</v>
+        <v>0.75</v>
       </c>
       <c r="R30" t="n">
         <v>10.8</v>
       </c>
       <c r="S30" t="n">
-        <v>30.8</v>
+        <v>30.7</v>
       </c>
       <c r="T30" t="n">
         <v>41.5</v>
@@ -5814,7 +5881,7 @@
         <v>14.6</v>
       </c>
       <c r="W30" t="n">
-        <v>6.8</v>
+        <v>6.9</v>
       </c>
       <c r="X30" t="n">
         <v>4.7</v>
@@ -5823,7 +5890,7 @@
         <v>4.8</v>
       </c>
       <c r="Z30" t="n">
-        <v>20.9</v>
+        <v>20.8</v>
       </c>
       <c r="AA30" t="n">
         <v>20.4</v>
@@ -5832,22 +5899,22 @@
         <v>94.8</v>
       </c>
       <c r="AC30" t="n">
-        <v>-5.5</v>
+        <v>-5.6</v>
       </c>
       <c r="AD30" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="AE30" t="n">
         <v>23</v>
       </c>
       <c r="AF30" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AG30" t="n">
         <v>23</v>
       </c>
       <c r="AH30" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AI30" t="n">
         <v>26</v>
@@ -5856,13 +5923,13 @@
         <v>26</v>
       </c>
       <c r="AK30" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AL30" t="n">
         <v>22</v>
       </c>
       <c r="AM30" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AN30" t="n">
         <v>17</v>
@@ -5895,13 +5962,13 @@
         <v>26</v>
       </c>
       <c r="AX30" t="n">
+        <v>17</v>
+      </c>
+      <c r="AY30" t="n">
         <v>16</v>
       </c>
-      <c r="AY30" t="n">
-        <v>18</v>
-      </c>
       <c r="AZ30" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BA30" t="n">
         <v>16</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>3-2-2013-14</t>
+          <t>2014-03-02</t>
         </is>
       </c>
     </row>
@@ -6017,7 +6084,7 @@
         <v>0.8</v>
       </c>
       <c r="AD31" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AE31" t="n">
         <v>14</v>
@@ -6044,16 +6111,16 @@
         <v>15</v>
       </c>
       <c r="AM31" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AN31" t="n">
         <v>2</v>
       </c>
       <c r="AO31" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AP31" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AQ31" t="n">
         <v>26</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>3-2-2013-14</t>
+          <t>2014-03-02</t>
         </is>
       </c>
     </row>
